--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5162,7 +5162,7 @@
         <v>46269</v>
       </c>
       <c r="B597">
-        <v>6.709125</v>
+        <v>6.707285000000001</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B597"/>
+  <dimension ref="A1:B598"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -5165,6 +5165,14 @@
         <v>6.707285000000001</v>
       </c>
     </row>
+    <row r="598" spans="1:2">
+      <c r="A598" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B598">
+        <v>6.708855</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5170,7 +5170,7 @@
         <v>46276</v>
       </c>
       <c r="B598">
-        <v>6.708855</v>
+        <v>6.704045</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5170,7 +5170,7 @@
         <v>46276</v>
       </c>
       <c r="B598">
-        <v>6.704045</v>
+        <v>6.709215</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5170,7 +5170,7 @@
         <v>46276</v>
       </c>
       <c r="B598">
-        <v>6.709215</v>
+        <v>6.708905</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5170,7 +5170,7 @@
         <v>46276</v>
       </c>
       <c r="B598">
-        <v>6.708905</v>
+        <v>6.707825</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B598"/>
+  <dimension ref="A1:B599"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -5173,6 +5173,14 @@
         <v>6.707825</v>
       </c>
     </row>
+    <row r="599" spans="1:2">
+      <c r="A599" s="3">
+        <v>46283</v>
+      </c>
+      <c r="B599">
+        <v>6.712825</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5178,7 +5178,7 @@
         <v>46283</v>
       </c>
       <c r="B599">
-        <v>6.712825</v>
+        <v>6.7079</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5178,7 +5178,7 @@
         <v>46283</v>
       </c>
       <c r="B599">
-        <v>6.7079</v>
+        <v>6.705825</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5178,7 +5178,7 @@
         <v>46283</v>
       </c>
       <c r="B599">
-        <v>6.705825</v>
+        <v>6.69815</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5178,7 +5178,7 @@
         <v>46283</v>
       </c>
       <c r="B599">
-        <v>6.69815</v>
+        <v>6.696575</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B599"/>
+  <dimension ref="A1:B600"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -5181,6 +5181,14 @@
         <v>6.696575</v>
       </c>
     </row>
+    <row r="600" spans="1:2">
+      <c r="A600" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B600">
+        <v>6.69862</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5186,7 +5186,7 @@
         <v>46290</v>
       </c>
       <c r="B600">
-        <v>6.69862</v>
+        <v>6.706895</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5186,7 +5186,7 @@
         <v>46290</v>
       </c>
       <c r="B600">
-        <v>6.706895</v>
+        <v>6.71509</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5186,7 +5186,7 @@
         <v>46290</v>
       </c>
       <c r="B600">
-        <v>6.71509</v>
+        <v>6.722295</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5186,7 +5186,7 @@
         <v>46290</v>
       </c>
       <c r="B600">
-        <v>6.722295</v>
+        <v>6.722455</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B600"/>
+  <dimension ref="A1:B601"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -5189,6 +5189,14 @@
         <v>6.722455</v>
       </c>
     </row>
+    <row r="601" spans="1:2">
+      <c r="A601" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B601">
+        <v>6.70401</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5194,7 +5194,7 @@
         <v>46297</v>
       </c>
       <c r="B601">
-        <v>6.70401</v>
+        <v>6.707165</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5194,7 +5194,7 @@
         <v>46297</v>
       </c>
       <c r="B601">
-        <v>6.707165</v>
+        <v>6.71654</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5194,7 +5194,7 @@
         <v>46297</v>
       </c>
       <c r="B601">
-        <v>6.71654</v>
+        <v>6.707825</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5194,7 +5194,7 @@
         <v>46297</v>
       </c>
       <c r="B601">
-        <v>6.707825</v>
+        <v>6.70615</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B601"/>
+  <dimension ref="A1:B602"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -5197,6 +5197,14 @@
         <v>6.70615</v>
       </c>
     </row>
+    <row r="602" spans="1:2">
+      <c r="A602" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B602">
+        <v>6.702685000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5202,7 +5202,7 @@
         <v>46304</v>
       </c>
       <c r="B602">
-        <v>6.702685000000001</v>
+        <v>6.70457</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5194,7 +5194,7 @@
         <v>46297</v>
       </c>
       <c r="B601">
-        <v>6.70615</v>
+        <v>6.70641</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -5202,7 +5202,7 @@
         <v>46304</v>
       </c>
       <c r="B602">
-        <v>6.70457</v>
+        <v>6.69229</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5194,7 +5194,7 @@
         <v>46297</v>
       </c>
       <c r="B601">
-        <v>6.70641</v>
+        <v>6.70615</v>
       </c>
     </row>
     <row r="602" spans="1:2">

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5194,7 +5194,7 @@
         <v>46297</v>
       </c>
       <c r="B601">
-        <v>6.70615</v>
+        <v>6.70641</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -5202,7 +5202,7 @@
         <v>46304</v>
       </c>
       <c r="B602">
-        <v>6.69229</v>
+        <v>6.694155</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B602"/>
+  <dimension ref="A1:B603"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -5194,7 +5194,7 @@
         <v>46297</v>
       </c>
       <c r="B601">
-        <v>6.70615</v>
+        <v>6.70641</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -5203,6 +5203,14 @@
       </c>
       <c r="B602">
         <v>6.694155</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B603">
+        <v>6.69204</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5194,7 +5194,7 @@
         <v>46297</v>
       </c>
       <c r="B601">
-        <v>6.70615</v>
+        <v>6.70641</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -5210,7 +5210,7 @@
         <v>46311</v>
       </c>
       <c r="B603">
-        <v>6.69204</v>
+        <v>6.69399</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B603"/>
+  <dimension ref="A1:B602"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -5194,7 +5194,7 @@
         <v>46297</v>
       </c>
       <c r="B601">
-        <v>6.70641</v>
+        <v>6.70615</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -5203,14 +5203,6 @@
       </c>
       <c r="B602">
         <v>6.694155</v>
-      </c>
-    </row>
-    <row r="603" spans="1:2">
-      <c r="A603" s="3">
-        <v>46311</v>
-      </c>
-      <c r="B603">
-        <v>6.69399</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B602"/>
+  <dimension ref="A1:B603"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -5194,7 +5194,7 @@
         <v>46297</v>
       </c>
       <c r="B601">
-        <v>6.70615</v>
+        <v>6.70641</v>
       </c>
     </row>
     <row r="602" spans="1:2">
@@ -5203,6 +5203,14 @@
       </c>
       <c r="B602">
         <v>6.694155</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B603">
+        <v>6.691795</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/USDCNH_diff_0th_diff.xlsx
+++ b/public/data/files/USDCNH_diff_0th_diff.xlsx
@@ -5210,7 +5210,7 @@
         <v>46311</v>
       </c>
       <c r="B603">
-        <v>6.691795</v>
+        <v>6.684645</v>
       </c>
     </row>
   </sheetData>
